--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N19_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.28045545437827</v>
+        <v>3.295574011336469</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42532215422878</v>
+        <v>3.481614850062177</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
